--- a/liq_calc/output/irrbb_report.xlsx
+++ b/liq_calc/output/irrbb_report.xlsx
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E2" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -534,28 +534,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E3" t="n">
-        <v>517747697.84</v>
+        <v>593802656.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-56701322.40000004</v>
+        <v>1003055.190000057</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.725110200000003</v>
+        <v>0.05572528833333652</v>
       </c>
       <c r="H3" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I3" t="n">
-        <v>1962409570.14</v>
+        <v>2768916924.63</v>
       </c>
       <c r="J3" t="n">
-        <v>-234333383.05</v>
+        <v>903325.0700001717</v>
       </c>
       <c r="K3" t="n">
-        <v>-19.52778192083333</v>
+        <v>0.05018472611112065</v>
       </c>
     </row>
     <row r="4">
@@ -573,28 +573,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E4" t="n">
-        <v>461504931.47</v>
+        <v>550757802.72</v>
       </c>
       <c r="F4" t="n">
-        <v>-112944088.77</v>
+        <v>-42041798.58999991</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.412007397499998</v>
+        <v>-2.335655477222217</v>
       </c>
       <c r="H4" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I4" t="n">
-        <v>2036311588.56</v>
+        <v>2975572356.07</v>
       </c>
       <c r="J4" t="n">
-        <v>-160431364.6300001</v>
+        <v>207558756.5100002</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.36928038583334</v>
+        <v>11.53104202833335</v>
       </c>
     </row>
     <row r="5">
@@ -612,28 +612,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E5" t="n">
-        <v>572113345.53</v>
+        <v>634633666.41</v>
       </c>
       <c r="F5" t="n">
-        <v>-2335674.710000038</v>
+        <v>41834065.10000002</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1946395591666699</v>
+        <v>2.324114727777779</v>
       </c>
       <c r="H5" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I5" t="n">
-        <v>1942212688.46</v>
+        <v>2669863190.42</v>
       </c>
       <c r="J5" t="n">
-        <v>-254530264.73</v>
+        <v>-98150409.13999987</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.21085539416667</v>
+        <v>-5.452800507777771</v>
       </c>
     </row>
     <row r="6">
@@ -651,28 +651,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E6" t="n">
-        <v>544755925.66</v>
+        <v>613562440.08</v>
       </c>
       <c r="F6" t="n">
-        <v>-29693094.58000004</v>
+        <v>20762838.7700001</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.474424548333337</v>
+        <v>1.153491042777783</v>
       </c>
       <c r="H6" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1986434749.04</v>
+        <v>2785181870.94</v>
       </c>
       <c r="J6" t="n">
-        <v>-210308204.1500001</v>
+        <v>17168271.38000011</v>
       </c>
       <c r="K6" t="n">
-        <v>-17.52568367916668</v>
+        <v>0.9537928544444508</v>
       </c>
     </row>
     <row r="7">
@@ -690,28 +690,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E7" t="n">
-        <v>494682929.06</v>
+        <v>575947127.49</v>
       </c>
       <c r="F7" t="n">
-        <v>-79766091.18000001</v>
+        <v>-16852473.81999993</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.647174265000001</v>
+        <v>-0.9362485455555519</v>
       </c>
       <c r="H7" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I7" t="n">
-        <v>2005579813.89</v>
+        <v>2878978573.31</v>
       </c>
       <c r="J7" t="n">
-        <v>-191163139.3</v>
+        <v>110964973.75</v>
       </c>
       <c r="K7" t="n">
-        <v>-15.93026160833333</v>
+        <v>6.164720763888889</v>
       </c>
     </row>
     <row r="8">
@@ -729,28 +729,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E8" t="n">
-        <v>523252522.32</v>
+        <v>597220617.66</v>
       </c>
       <c r="F8" t="n">
-        <v>-51196497.92000002</v>
+        <v>4421016.350000024</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.266374826666668</v>
+        <v>0.2456120194444457</v>
       </c>
       <c r="H8" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I8" t="n">
-        <v>2007557927.9</v>
+        <v>2850719213.32</v>
       </c>
       <c r="J8" t="n">
-        <v>-189185025.29</v>
+        <v>82705613.76000023</v>
       </c>
       <c r="K8" t="n">
-        <v>-15.76541877416667</v>
+        <v>4.594756320000013</v>
       </c>
     </row>
     <row r="9">
@@ -768,28 +768,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E9" t="n">
-        <v>488894215.92</v>
+        <v>571902395.28</v>
       </c>
       <c r="F9" t="n">
-        <v>-85554804.31999999</v>
+        <v>-20897206.02999997</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.129567026666667</v>
+        <v>-1.160955890555554</v>
       </c>
       <c r="H9" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I9" t="n">
-        <v>1986981024.26</v>
+        <v>2849113659.19</v>
       </c>
       <c r="J9" t="n">
-        <v>-209761928.9300001</v>
+        <v>81100059.63000011</v>
       </c>
       <c r="K9" t="n">
-        <v>-17.48016074416667</v>
+        <v>4.50555886833334</v>
       </c>
     </row>
     <row r="10">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E10" t="n">
-        <v>461504931.47</v>
+        <v>550757802.72</v>
       </c>
       <c r="F10" t="n">
-        <v>-112944088.77</v>
+        <v>-42041798.58999991</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.412007397499998</v>
+        <v>-2.335655477222217</v>
       </c>
       <c r="H10" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2036311588.56</v>
+        <v>2975572356.07</v>
       </c>
       <c r="J10" t="n">
-        <v>-160431364.6300001</v>
+        <v>207558756.5100002</v>
       </c>
       <c r="K10" t="n">
-        <v>-13.36928038583334</v>
+        <v>11.53104202833335</v>
       </c>
     </row>
     <row r="11">
@@ -846,28 +846,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E11" t="n">
-        <v>572113345.53</v>
+        <v>634633666.41</v>
       </c>
       <c r="F11" t="n">
-        <v>-2335674.710000038</v>
+        <v>41834065.10000002</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1946395591666699</v>
+        <v>2.324114727777779</v>
       </c>
       <c r="H11" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I11" t="n">
-        <v>1942212688.46</v>
+        <v>2669863190.42</v>
       </c>
       <c r="J11" t="n">
-        <v>-254530264.73</v>
+        <v>-98150409.13999987</v>
       </c>
       <c r="K11" t="n">
-        <v>-21.21085539416667</v>
+        <v>-5.452800507777771</v>
       </c>
     </row>
   </sheetData>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E2" t="n">
-        <v>461504931.47</v>
+        <v>550757802.72</v>
       </c>
       <c r="F2" t="n">
-        <v>-112944088.77</v>
+        <v>-42041798.58999991</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.412007397499998</v>
+        <v>-2.335655477222217</v>
       </c>
       <c r="H2" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2036311588.56</v>
+        <v>2975572356.07</v>
       </c>
       <c r="J2" t="n">
-        <v>-160431364.6300001</v>
+        <v>207558756.5100002</v>
       </c>
       <c r="K2" t="n">
-        <v>-13.36928038583334</v>
+        <v>11.53104202833335</v>
       </c>
     </row>
     <row r="3">
@@ -995,28 +995,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E3" t="n">
-        <v>572113345.53</v>
+        <v>634633666.41</v>
       </c>
       <c r="F3" t="n">
-        <v>-2335674.710000038</v>
+        <v>41834065.10000002</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1946395591666699</v>
+        <v>2.324114727777779</v>
       </c>
       <c r="H3" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="I3" t="n">
-        <v>1942212688.46</v>
+        <v>2669863190.42</v>
       </c>
       <c r="J3" t="n">
-        <v>-254530264.73</v>
+        <v>-98150409.13999987</v>
       </c>
       <c r="K3" t="n">
-        <v>-21.21085539416667</v>
+        <v>-5.452800507777771</v>
       </c>
     </row>
   </sheetData>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D2" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D3" t="n">
-        <v>523252522.32</v>
+        <v>597220617.66</v>
       </c>
       <c r="E3" t="n">
-        <v>-51196497.92000002</v>
+        <v>4421016.350000024</v>
       </c>
     </row>
     <row r="4">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D4" t="n">
-        <v>494682929.06</v>
+        <v>575947127.49</v>
       </c>
       <c r="E4" t="n">
-        <v>-79766091.18000001</v>
+        <v>-16852473.81999993</v>
       </c>
     </row>
     <row r="5">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D5" t="n">
-        <v>461504931.47</v>
+        <v>550757802.72</v>
       </c>
       <c r="E5" t="n">
-        <v>-112944088.77</v>
+        <v>-42041798.58999991</v>
       </c>
     </row>
     <row r="6">
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D6" t="n">
-        <v>572113345.53</v>
+        <v>634633666.41</v>
       </c>
       <c r="E6" t="n">
-        <v>-2335674.710000038</v>
+        <v>41834065.10000002</v>
       </c>
     </row>
     <row r="7">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D7" t="n">
-        <v>488894215.92</v>
+        <v>571902395.28</v>
       </c>
       <c r="E7" t="n">
-        <v>-85554804.31999999</v>
+        <v>-20897206.02999997</v>
       </c>
     </row>
     <row r="8">
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D8" t="n">
-        <v>544755925.66</v>
+        <v>613562440.08</v>
       </c>
       <c r="E8" t="n">
-        <v>-29693094.58000004</v>
+        <v>20762838.7700001</v>
       </c>
     </row>
     <row r="9">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D9" t="n">
-        <v>517747697.84</v>
+        <v>593802656.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-56701322.40000004</v>
+        <v>1003055.190000057</v>
       </c>
     </row>
     <row r="10">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D10" t="n">
-        <v>572113345.53</v>
+        <v>634633666.41</v>
       </c>
       <c r="E10" t="n">
-        <v>-2335674.710000038</v>
+        <v>41834065.10000002</v>
       </c>
     </row>
     <row r="11">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>574449020.24</v>
+        <v>592799601.3099999</v>
       </c>
       <c r="D11" t="n">
-        <v>461504931.47</v>
+        <v>550757802.72</v>
       </c>
       <c r="E11" t="n">
-        <v>-112944088.77</v>
+        <v>-42041798.58999991</v>
       </c>
     </row>
   </sheetData>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D2" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D3" t="n">
-        <v>2007557927.9</v>
+        <v>2850719213.32</v>
       </c>
       <c r="E3" t="n">
-        <v>-189185025.29</v>
+        <v>82705613.76000023</v>
       </c>
     </row>
     <row r="4">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D4" t="n">
-        <v>2005579813.89</v>
+        <v>2878978573.31</v>
       </c>
       <c r="E4" t="n">
-        <v>-191163139.3</v>
+        <v>110964973.75</v>
       </c>
     </row>
     <row r="5">
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D5" t="n">
-        <v>2036311588.56</v>
+        <v>2975572356.07</v>
       </c>
       <c r="E5" t="n">
-        <v>-160431364.6300001</v>
+        <v>207558756.5100002</v>
       </c>
     </row>
     <row r="6">
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D6" t="n">
-        <v>1942212688.46</v>
+        <v>2669863190.42</v>
       </c>
       <c r="E6" t="n">
-        <v>-254530264.73</v>
+        <v>-98150409.13999987</v>
       </c>
     </row>
     <row r="7">
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D7" t="n">
-        <v>1986981024.26</v>
+        <v>2849113659.19</v>
       </c>
       <c r="E7" t="n">
-        <v>-209761928.9300001</v>
+        <v>81100059.63000011</v>
       </c>
     </row>
     <row r="8">
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D8" t="n">
-        <v>1986434749.04</v>
+        <v>2785181870.94</v>
       </c>
       <c r="E8" t="n">
-        <v>-210308204.1500001</v>
+        <v>17168271.38000011</v>
       </c>
     </row>
     <row r="9">
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D9" t="n">
-        <v>1962409570.14</v>
+        <v>2768916924.63</v>
       </c>
       <c r="E9" t="n">
-        <v>-234333383.05</v>
+        <v>903325.0700001717</v>
       </c>
     </row>
     <row r="10">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D10" t="n">
-        <v>1942212688.46</v>
+        <v>2669863190.42</v>
       </c>
       <c r="E10" t="n">
-        <v>-254530264.73</v>
+        <v>-98150409.13999987</v>
       </c>
     </row>
     <row r="11">
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2196742953.19</v>
+        <v>2768013599.56</v>
       </c>
       <c r="D11" t="n">
-        <v>2036311588.56</v>
+        <v>2975572356.07</v>
       </c>
       <c r="E11" t="n">
-        <v>-160431364.6300001</v>
+        <v>207558756.5100002</v>
       </c>
     </row>
   </sheetData>
